--- a/MLOps/ROADMAP.xlsx
+++ b/MLOps/ROADMAP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hi\Desktop\projects\python_projects\tutorial\tut_youtube\MLOps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3740BD33-ACE2-4859-A731-07E868CC3D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC30D927-41B1-4FC9-9D9E-7CC63973E11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1185" yWindow="2775" windowWidth="27615" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="166">
   <si>
     <t>Phase</t>
   </si>
@@ -520,6 +520,9 @@
   </si>
   <si>
     <t>pdf+code+video done</t>
+  </si>
+  <si>
+    <t>pdf done</t>
   </si>
 </sst>
 </file>
@@ -630,8 +633,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G45" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="B1:G45" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}" name="Table1" displayName="Table1" ref="B1:G47" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="B1:G47" xr:uid="{B1547D38-DD11-41AC-A766-B97FCF653AE0}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C1EF5561-1CEA-475F-8C66-9F535CF497F6}" name="Phase" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{B40C6DFB-4AB1-4F8D-9C13-F15D2B3BFA57}" name="Module" dataDxfId="4"/>
@@ -907,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
@@ -1239,46 +1242,31 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>163</v>
@@ -1286,380 +1274,377 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>73</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G32" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="G37" s="2"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G38" s="2"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>138</v>
-      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1667,16 +1652,16 @@
         <v>130</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G40" s="2"/>
     </row>
@@ -1685,61 +1670,61 @@
         <v>130</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>155</v>
-      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1747,18 +1732,54 @@
         <v>147</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G45" s="2"/>
+      <c r="G47" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
